--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K57.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K57.xlsx
@@ -99,7 +99,7 @@
     <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
   </si>
   <si>
-    <t>Các dòng có nhiều tên ngành mâu thuẫn không được đưa vào sheet import và nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
   </si>
 </sst>
 </file>

--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K57.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K57.xlsx
@@ -6,14 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="Khoa nganh dao tao" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Đối chiếu nguồn" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Nguồn chỉ tiêu" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>Khoá ngành đào tạo</t>
   </si>
@@ -21,7 +22,7 @@
     <t>Ngành đào tạo</t>
   </si>
   <si>
-    <t>Số lượng sinh viên</t>
+    <t>Số lượng sinh viên đầu vào</t>
   </si>
   <si>
     <t>ĐTV57ĐH</t>
@@ -78,35 +79,116 @@
     <t>Kết luận</t>
   </si>
   <si>
+    <t>Mã CTĐT tuyển sinh</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu công bố</t>
+  </si>
+  <si>
+    <t>Số đầu vào tạm tính áp dụng</t>
+  </si>
+  <si>
+    <t>Căn cứ áp dụng</t>
+  </si>
+  <si>
     <t>K57</t>
   </si>
   <si>
     <t>Đủ điều kiện import</t>
   </si>
   <si>
+    <t>D104</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh công bố</t>
+  </si>
+  <si>
+    <t>A408</t>
+  </si>
+  <si>
+    <t>A409</t>
+  </si>
+  <si>
+    <t>D127</t>
+  </si>
+  <si>
+    <t>D122</t>
+  </si>
+  <si>
+    <t>D119</t>
+  </si>
+  <si>
+    <t>THÔNG TIN NGUỒN</t>
+  </si>
+  <si>
+    <t>GIÁ TRỊ</t>
+  </si>
+  <si>
+    <t>Khóa</t>
+  </si>
+  <si>
+    <t>Năm tuyển sinh</t>
+  </si>
+  <si>
+    <t>Loại dữ liệu</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh dùng làm số đầu vào tạm tính; KHÔNG phải số sinh viên thực nhập</t>
+  </si>
+  <si>
+    <t>Loại nguồn</t>
+  </si>
+  <si>
+    <t>official_admission_announcement</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>https://tuyensinh.vimaru.edu.vn/node/210</t>
+  </si>
+  <si>
+    <t>Nguyên tắc</t>
+  </si>
+  <si>
+    <t>Số áp dụng = max(chỉ tiêu công bố, số sinh viên tốt nghiệp duy nhất đã quan sát) để không tạo tỷ lệ tốt nghiệp vượt 100%</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Thay bằng số thực nhập chính thức khi Nhà trường cung cấp dữ liệu.</t>
+  </si>
+  <si>
     <t>HƯỚNG DẪN</t>
   </si>
   <si>
-    <t>Khi import, chọn đúng K57 ở trường “Import vào khoá học”.</t>
+    <t>Khi import, chọn đúng K57 ở trường “Import vào khóa học”.</t>
+  </si>
+  <si>
+    <t>File này chỉ được chứa mã lớp của K57; hệ thống sẽ từ chối file chứa từ hai khóa trở lên.</t>
   </si>
   <si>
     <t>Sheet “Khoa nganh dao tao” là dữ liệu import; hệ thống chỉ đọc sheet đầu tiên.</t>
   </si>
   <si>
-    <t>Số lượng sinh viên trong file này là số mã sinh viên duy nhất quan sát được trong các file tốt nghiệp nguồn.</t>
-  </si>
-  <si>
-    <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
-  </si>
-  <si>
-    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Cột số lượng sinh viên đầu vào hiện dùng chỉ tiêu tuyển sinh công bố làm dữ liệu tạm tính, không phải số thực nhập.</t>
+  </si>
+  <si>
+    <t>Nếu số tốt nghiệp quan sát được lớn hơn chỉ tiêu, file dùng số tốt nghiệp làm cận dưới để tránh tỷ lệ vượt 100%.</t>
+  </si>
+  <si>
+    <t>Xem nguồn, năm công bố và nguyên tắc áp dụng tại sheet “Nguồn chỉ tiêu”.</t>
+  </si>
+  <si>
+    <t>Cần thay dữ liệu tạm tính bằng số thực nhập khi Nhà trường cung cấp dữ liệu chính thức.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -117,9 +199,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
     </font>
     <font>
       <b/>
@@ -151,13 +230,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,10 +589,10 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,7 +611,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -535,7 +622,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -546,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -557,7 +644,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -568,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -579,19 +666,19 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -600,31 +687,46 @@
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="70" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -639,12 +741,24 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -659,12 +773,24 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -679,12 +805,24 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -699,12 +837,24 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -719,12 +869,24 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>45</v>
+      </c>
+      <c r="I6">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -739,52 +901,153 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>45</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="115" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="100" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
